--- a/backtest_runs/20260410_193731/by_symbol/HPL/HPL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/HPL/HPL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
         <v>-2969.000000000005</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>100068.75</v>
@@ -633,7 +633,7 @@
         <v>-743.0000000000064</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>99325.75</v>
@@ -679,7 +679,7 @@
         <v>-3576.249999999993</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>95749.5</v>
@@ -725,7 +725,7 @@
         <v>-706.0000000000059</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>95043.5</v>
@@ -1047,7 +1047,7 @@
         <v>-955.9999999999945</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>98876.5</v>
@@ -1185,7 +1185,7 @@
         <v>-862.9999999999882</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>105467</v>
@@ -1231,7 +1231,7 @@
         <v>-1170.25000000001</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>104296.75</v>
@@ -1277,7 +1277,7 @@
         <v>-1216.750000000002</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>103080</v>
@@ -1369,7 +1369,7 @@
         <v>-4005.500000000006</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>99654.25</v>
@@ -1415,7 +1415,7 @@
         <v>-1757.000000000005</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>97897.25</v>
@@ -1461,7 +1461,7 @@
         <v>-290.9999999999968</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>97606.25</v>
@@ -1507,7 +1507,7 @@
         <v>-455.5000000000064</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>97150.75</v>
@@ -1553,7 +1553,7 @@
         <v>-246.4999999999918</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>96904.25</v>
@@ -1645,7 +1645,7 @@
         <v>-1047.249999999997</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>98903.5</v>
